--- a/mydata.xlsx
+++ b/mydata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/da27eec1915becc9/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saira\dear-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{535FDD98-EA56-495F-8EE2-2A0BA89872B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBC0B4FF-B354-4CAC-8E57-9A5FCDC909F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{585CB737-E687-43DE-A097-C371930CAC41}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>no. of charms</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>hirono</t>
+  </si>
+  <si>
+    <t>hirono, haikyuu, kpop</t>
   </si>
 </sst>
 </file>
@@ -453,13 +456,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7692367D-2D7D-48E0-9323-E4EA285BA096}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -518,6 +521,17 @@
       </c>
       <c r="D5" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
